--- a/CELAB4/Robust S9)/Parameters to test.xlsx
+++ b/CELAB4/Robust S9)/Parameters to test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmm1\Documents\GitHub\CELAB\CELAB4\Robust S9)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D852FD9-D630-4CF6-B6D2-EF9DB654AC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEEE8395-9563-4FBC-8CD5-7668DC2E7C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{DDDC5A2A-72B8-434B-953D-3E4654877846}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{DDDC5A2A-72B8-434B-953D-3E4654877846}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
